--- a/测试集/泛用性验收_v3/W2/W2_预期_1月汇总.xlsx
+++ b/测试集/泛用性验收_v3/W2/W2_预期_1月汇总.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +52,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,17 +442,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>责任单位</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>任务名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>1月数量</t>
         </is>
@@ -441,11 +466,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>完成年度预算编制</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -456,11 +481,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +500,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +515,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -501,11 +526,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>组织安全培训演练</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
@@ -516,11 +541,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -531,11 +556,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -546,11 +571,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -561,11 +586,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>完成年度预算</t>
+          <t>设备巡检维护</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -576,11 +601,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>组织安全培训</t>
+          <t>季度报表汇总</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -591,11 +616,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>设备巡检维护</t>
+          <t>完成资料汇总</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -606,11 +631,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>季度报表汇总</t>
+          <t>成本合计核算</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
